--- a/results/Int Task Remove ACC -0.7/Rando_10_permute.xlsx
+++ b/results/Int Task Remove ACC -0.7/Rando_10_permute.xlsx
@@ -440,327 +440,327 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6608652487712805</v>
+        <v>0.6576641111575405</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6733386348066597</v>
+        <v>0.6576641111575405</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6701215074945492</v>
+        <v>0.649138759313111</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6695842536293062</v>
+        <v>0.6572974140749142</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6912392797955593</v>
+        <v>0.6581203505510405</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6936149936467598</v>
+        <v>0.6593014562706623</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.710122402917658</v>
+        <v>0.656211891218884</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7129568434487719</v>
+        <v>0.6552969251454708</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7157777815679285</v>
+        <v>0.6571268572922974</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7279274650429661</v>
+        <v>0.6594780536059968</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7256007862667678</v>
+        <v>0.6547376410291397</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7253591641580606</v>
+        <v>0.6693145607167934</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7225492411644481</v>
+        <v>0.6606346417881173</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7260055032988524</v>
+        <v>0.6658803288334769</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7547581789083797</v>
+        <v>0.6573500024162211</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7501673588429427</v>
+        <v>0.6692850686064657</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7493284326684462</v>
+        <v>0.6817413989635833</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7293807509615138</v>
+        <v>0.6889200628786005</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7551053330263311</v>
+        <v>0.6889580828280588</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7483214369977458</v>
+        <v>0.68051978600809</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7313773312980224</v>
+        <v>0.6852601985849471</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7333863480665967</v>
+        <v>0.6548186555008826</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7333863480665967</v>
+        <v>0.6494184013712765</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6914279582363292</v>
+        <v>0.6497360633789004</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6914009534124148</v>
+        <v>0.6956264977017473</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6719756018522467</v>
+        <v>0.699107277373653</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6717339797435395</v>
+        <v>0.7047196615016388</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6601300779728758</v>
+        <v>0.7032049040760229</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6819812444391382</v>
+        <v>0.6803993302803669</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6915601397428572</v>
+        <v>0.7031029253330832</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6615218923843553</v>
+        <v>0.7067738047522805</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6551931697693788</v>
+        <v>0.7105722464318099</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6403611255610607</v>
+        <v>0.7095517483491525</v>
       </c>
     </row>
     <row r="35">
@@ -770,557 +770,557 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6588345570782486</v>
+        <v>0.6967397360349528</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.654996674142739</v>
+        <v>0.6776014883921897</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6543993700769495</v>
+        <v>0.6707625167358843</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6454888441651103</v>
+        <v>0.6753213574045805</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6549991614291522</v>
+        <v>0.6649035359263649</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6905002004042196</v>
+        <v>0.6372655199565649</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.690220558346054</v>
+        <v>0.6454106723064109</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6851244638121147</v>
+        <v>0.6506343291006825</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7003416820878424</v>
+        <v>0.650037025034893</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6885992029313026</v>
+        <v>0.6265165340587682</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6885992029313026</v>
+        <v>0.6302279207138369</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6853220254186458</v>
+        <v>0.6290112823311701</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6566134103112946</v>
+        <v>0.600588349834702</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.666572505109597</v>
+        <v>0.6019215353521571</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6503642808615392</v>
+        <v>0.5799598623038242</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.67044449940163</v>
+        <v>0.5627595661035451</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6169738820713553</v>
+        <v>0.6022502124853251</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6103385125742988</v>
+        <v>0.5722428785436725</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6192000034111357</v>
+        <v>0.5649281245291922</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6262670947641911</v>
+        <v>0.5649281245291922</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.661262859270756</v>
+        <v>0.5657400458797746</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6217277970601696</v>
+        <v>0.5985317192976471</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6253251238668633</v>
+        <v>0.599715312303682</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6212065328932969</v>
+        <v>0.6185494003507784</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6215917069607065</v>
+        <v>0.6220056624851829</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6315937962812936</v>
+        <v>0.6068474284301101</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5921507636679941</v>
+        <v>0.5721128289969271</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5245129182549767</v>
+        <v>0.5730167799447965</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5232667877619823</v>
+        <v>0.5608500407914971</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.520163720298247</v>
+        <v>0.5703148762468411</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.503433165903425</v>
+        <v>0.5703148762468411</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4994851317124754</v>
+        <v>0.6720185963745313</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4994851317124754</v>
+        <v>0.6387632217039192</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5044426488605386</v>
+        <v>0.6197990841100773</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5181834849867393</v>
+        <v>0.5980815204568648</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5273342117007638</v>
+        <v>0.583368510669748</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5209429515988276</v>
+        <v>0.5850833169883083</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5203211299955371</v>
+        <v>0.5820452742979456</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5203211299955371</v>
+        <v>0.5820452742979456</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5102565031879905</v>
+        <v>0.5067647083905409</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5428591428384628</v>
+        <v>0.5021273405365148</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6151162344473534</v>
+        <v>0.5245377911191084</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6044503949810824</v>
+        <v>0.5237553618788535</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5997700326047716</v>
+        <v>0.5167618231383017</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.623445090665143</v>
+        <v>0.5162540613833861</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.588092222894974</v>
+        <v>0.5367350883626265</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5869736546623118</v>
+        <v>0.5367350883626265</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5357540315359491</v>
+        <v>0.5366970684131681</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5326609132178663</v>
+        <v>0.5028383491240488</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5452742979456435</v>
+        <v>0.4987908234765726</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5203456475330384</v>
+        <v>0.4948992862198648</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5107237577070346</v>
+        <v>0.490572118514223</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5077617549155886</v>
+        <v>0.4906431838403134</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5077617549155886</v>
+        <v>0.4994837104059535</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5006800951706847</v>
+        <v>0.4989489438271236</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.500044771155437</v>
+        <v>0.5024702307349008</v>
       </c>
     </row>
   </sheetData>
